--- a/experiments/results/resnet_imagenet34/ImageNet-1K/baseline/msp/adaptive/max/results.xlsx
+++ b/experiments/results/resnet_imagenet34/ImageNet-1K/baseline/msp/adaptive/max/results.xlsx
@@ -342,7 +342,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="11" max="11"/>
@@ -651,6 +651,43 @@
       <c r="K8" s="4" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=None,react_th=None,scale_th=10.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>63.65</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>83.73</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>67.61</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>81.64</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>89.12</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>90.23</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>57.61</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>86.18000000000001</v>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=None,scale_th=6.0,type=max</t>
         </is>
       </c>
     </row>
